--- a/reports/集团总公司_资产负债表_2026-02.xlsx
+++ b/reports/集团总公司_资产负债表_2026-02.xlsx
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0</v>
+        <v>6721780</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0</v>
+        <v>6748667</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0</v>
+        <v>7177040</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0</v>
+        <v>7205748</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0</v>
+        <v>8087560</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0</v>
+        <v>8119910</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0</v>
+        <v>10819120</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0</v>
+        <v>10862396</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0</v>
+        <v>11274380</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0</v>
+        <v>11319478</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0</v>
+        <v>11729640</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0</v>
+        <v>11776559</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0</v>
+        <v>14005940</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0</v>
+        <v>14061964</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>806802500</v>
+        <v>876617960</v>
       </c>
       <c r="G29" s="19" t="n"/>
     </row>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0</v>
+        <v>18558540</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0</v>
+        <v>18632774</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="F55" s="19" t="n">
-        <v>2336600000</v>
+        <v>2355158540</v>
       </c>
       <c r="G55" s="19" t="n"/>
     </row>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="F56" s="19" t="n">
-        <v>3143402500</v>
+        <v>3231776500</v>
       </c>
       <c r="G56" s="19" t="n"/>
     </row>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="F60" s="16" t="n">
-        <v>0</v>
+        <v>31761080</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>0</v>
+        <v>31888124</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1">
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="F62" s="16" t="n">
-        <v>0</v>
+        <v>32671600</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>0</v>
+        <v>32802287</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0</v>
+        <v>35403160</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0</v>
+        <v>35544772</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1">
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0</v>
+        <v>35858420</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0</v>
+        <v>36001854</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="F70" s="16" t="n">
-        <v>0</v>
+        <v>36313680</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0</v>
+        <v>36458934</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1">
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="F78" s="16" t="n">
-        <v>0</v>
+        <v>39955760</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>0</v>
+        <v>40115582</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1">
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0</v>
+        <v>40411020</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0</v>
+        <v>40572665</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="F84" s="19" t="n">
-        <v>332833700</v>
+        <v>585208420</v>
       </c>
       <c r="G84" s="19" t="n"/>
     </row>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="F86" s="16" t="n">
-        <v>0</v>
+        <v>43597840</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>0</v>
+        <v>43772232</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1">
@@ -5238,7 +5238,7 @@
         </is>
       </c>
       <c r="F98" s="19" t="n">
-        <v>529000000</v>
+        <v>572597840</v>
       </c>
       <c r="G98" s="19" t="n"/>
     </row>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="F99" s="19" t="n">
-        <v>861833700</v>
+        <v>1157806260</v>
       </c>
       <c r="G99" s="19" t="n"/>
     </row>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="F121" s="16" t="n">
-        <v>806568800</v>
+        <v>598970240</v>
       </c>
       <c r="G121" s="16" t="n">
         <v>897742928</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="F122" s="19" t="n">
-        <v>2281568800</v>
+        <v>2073970240</v>
       </c>
       <c r="G122" s="19" t="n"/>
     </row>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="F124" s="19" t="n">
-        <v>2281568800</v>
+        <v>2073970240</v>
       </c>
       <c r="G124" s="19" t="n"/>
     </row>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="F125" s="25" t="n">
-        <v>3143402500</v>
+        <v>3231776500</v>
       </c>
       <c r="G125" s="25" t="n"/>
     </row>
